--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536120_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536120_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,64 +1716,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1301</v>
+        <v>1.2862</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1301</v>
+        <v>1.5721</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1301</v>
+        <v>-0.4974</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3075</v>
+        <v>-2.2922</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8226</v>
+        <v>1.7948</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1301</v>
+        <v>0.9331</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3075</v>
+        <v>-1.529</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8226</v>
+        <v>2.4621</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.4305</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.7632</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3649</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.2203</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8439</v>
+        <v>-0.9673</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5579</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2859</v>
+        <v>-1.6866</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6275</v>
+        <v>2.6681</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5997</v>
+        <v>-0.6629</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0278</v>
+        <v>3.331</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.197</v>
+        <v>4.4447</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8365</v>
+        <v>1.1236</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6395999999999999</v>
+        <v>3.3211</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4305</v>
+        <v>-1.7767</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7632</v>
+        <v>-1.7865</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6673</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.195</v>
+        <v>-3.5097</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1699</v>
+        <v>-5.0696</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3649</v>
+        <v>1.5599</v>
       </c>
       <c r="S19" t="n">
-        <v>0.09</v>
+        <v>0.2058</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3103</v>
+        <v>0.4556</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2203</v>
+        <v>-0.2498</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4986</v>
+        <v>-0.3315</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4986</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9673</v>
+        <v>-1.3756</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.4212</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6866</v>
+        <v>-1.7969</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6681</v>
+        <v>-0.9559</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6629</v>
+        <v>-3.094</v>
       </c>
       <c r="I20" t="n">
-        <v>3.331</v>
+        <v>2.1381</v>
       </c>
       <c r="J20" t="n">
-        <v>4.4447</v>
+        <v>0.4106</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1236</v>
+        <v>-1.857</v>
       </c>
       <c r="L20" t="n">
-        <v>3.3211</v>
+        <v>2.2676</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7767</v>
+        <v>-1.3665</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7865</v>
+        <v>-1.237</v>
       </c>
       <c r="O20" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.1295</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.5097</v>
+        <v>1.3649</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.0696</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5599</v>
+        <v>1.3649</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2058</v>
+        <v>-0.0075</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4556</v>
+        <v>0.0106</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2498</v>
+        <v>-0.0181</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3315</v>
+        <v>-1.7772</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8885999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2201</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3756</v>
+        <v>-1.722</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4212</v>
+        <v>-1.3822</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7969</v>
+        <v>-0.3398</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9559</v>
+        <v>-2.8742</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.094</v>
+        <v>-0.844</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1381</v>
+        <v>-2.0302</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4106</v>
+        <v>-1.644</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.857</v>
+        <v>0.3895</v>
       </c>
       <c r="L21" t="n">
-        <v>2.2676</v>
+        <v>-2.0335</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3665</v>
+        <v>-1.2302</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.237</v>
+        <v>-1.2335</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1295</v>
+        <v>0.0033</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3649</v>
+        <v>0.7799</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3649</v>
+        <v>0.7799</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0075</v>
+        <v>0.3724</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0106</v>
+        <v>0.2618</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0181</v>
+        <v>0.1105</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7772</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7772</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,58 +2214,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.722</v>
+        <v>-1.7825</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3822</v>
+        <v>-2.5408</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3398</v>
+        <v>0.7583</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8742</v>
+        <v>-1.9674</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.844</v>
+        <v>-1.18</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0302</v>
+        <v>-0.7874</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.644</v>
+        <v>-1.5555</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3895</v>
+        <v>-1.037</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0335</v>
+        <v>-0.5185</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2302</v>
+        <v>-0.4119</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2335</v>
+        <v>-0.143</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0033</v>
+        <v>-0.2689</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7799</v>
+        <v>0.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7799</v>
+        <v>1.3649</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3724</v>
+        <v>-0.2051</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2618</v>
+        <v>-0.0104</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1105</v>
+        <v>-0.1947</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>R. ISSANZA TSHUKA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7825</v>
+        <v>-1.845</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5408</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7583</v>
+        <v>-2.5572</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9674</v>
+        <v>0.9853</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.18</v>
+        <v>1.4129</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7874</v>
+        <v>-0.4276</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5555</v>
+        <v>1.7317</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.037</v>
+        <v>1.4887</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5185</v>
+        <v>0.243</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4119</v>
+        <v>-0.7464</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.143</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2689</v>
+        <v>-0.6706</v>
       </c>
       <c r="P23" t="n">
-        <v>0.39</v>
+        <v>-0.585</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9749</v>
+        <v>-1.1699</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3649</v>
+        <v>0.585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2051</v>
+        <v>-0.0837</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0104</v>
+        <v>-0.1281</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1947</v>
+        <v>0.0444</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.1616</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. ISSANZA TSHUKA</t>
+          <t>J. PLEASANT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.845</v>
+        <v>-3.4539</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7122000000000001</v>
+        <v>-3.3387</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5572</v>
+        <v>-0.1152</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9853</v>
+        <v>-4.7478</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4129</v>
+        <v>-3.2022</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4276</v>
+        <v>-1.5456</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7317</v>
+        <v>-2.7695</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4887</v>
+        <v>-1.6189</v>
       </c>
       <c r="L24" t="n">
-        <v>0.243</v>
+        <v>-1.1505</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7464</v>
+        <v>-1.9784</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-1.5833</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6706</v>
+        <v>-0.3951</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.585</v>
+        <v>0.585</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.1699</v>
       </c>
       <c r="R24" t="n">
-        <v>0.585</v>
+        <v>1.7549</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0837</v>
+        <v>0.709</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1281</v>
+        <v>0.3221</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0444</v>
+        <v>0.3868</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1616</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0.2786</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4401</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. PLEASANT</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,152 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4539</v>
+        <v>-6.1218</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3387</v>
+        <v>-0.1761999999999992</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1152</v>
+        <v>-5.9457</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.7478</v>
+        <v>-6.274999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.2022</v>
+        <v>-10.2593</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5456</v>
+        <v>3.9844</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.7695</v>
+        <v>5.667599999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6189</v>
+        <v>-2.3172</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.1505</v>
+        <v>7.984900000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9784</v>
+        <v>-11.9428</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.5833</v>
+        <v>-7.9421</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3951</v>
+        <v>-4.0005</v>
       </c>
       <c r="P25" t="n">
-        <v>0.585</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1699</v>
+        <v>-12.674</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7549</v>
+        <v>12.6741</v>
       </c>
       <c r="S25" t="n">
-        <v>0.709</v>
+        <v>1.9305</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3221</v>
+        <v>2.0559</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3868</v>
+        <v>-0.1255</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.7773</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2786</v>
+        <v>4.7745</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536120_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-6.121799999999999</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.1760999999999995</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-5.945699999999999</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-6.274999999999999</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-10.2593</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.9844</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5.667600000000001</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-2.3172</v>
-      </c>
-      <c r="L26" t="n">
-        <v>7.985000000000002</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-11.9428</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-7.9421</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-4.0005</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-1.110223024625157e-16</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-12.674</v>
-      </c>
-      <c r="R26" t="n">
-        <v>12.6741</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.9305</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.0559</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.1255</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-1.7773</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.7745</v>
-      </c>
-      <c r="X26" t="n">
         <v>-6.5518</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
